--- a/data/trans_orig/P2B_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2007</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97656</t>
+          <t>98259</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>136251</t>
+          <t>136280</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>133137</t>
+          <t>131267</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>176196</t>
+          <t>172080</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>243620</t>
+          <t>242571</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>300766</t>
+          <t>298470</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>394101</t>
+          <t>394072</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>432696</t>
+          <t>432093</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>411368</t>
+          <t>415484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>454427</t>
+          <t>456297</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>817150</t>
+          <t>819446</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>874296</t>
+          <t>875345</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,3%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>147235</t>
+          <t>147572</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>193836</t>
+          <t>193840</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>195949</t>
+          <t>194743</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>244536</t>
+          <t>246826</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>350199</t>
+          <t>349270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>421187</t>
+          <t>424594</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>553789</t>
+          <t>553785</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>600390</t>
+          <t>600053</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>602064</t>
+          <t>599774</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>650651</t>
+          <t>651857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1173038</t>
+          <t>1169631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1244026</t>
+          <t>1244955</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,09%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90597</t>
+          <t>91281</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129184</t>
+          <t>128871</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128339</t>
+          <t>127624</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>170075</t>
+          <t>169927</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>231801</t>
+          <t>227862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>286343</t>
+          <t>285930</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>384647</t>
+          <t>384960</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423234</t>
+          <t>422550</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>412760</t>
+          <t>412908</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>454496</t>
+          <t>455211</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>810323</t>
+          <t>810736</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>864865</t>
+          <t>868804</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,22%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121507</t>
+          <t>123677</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>165082</t>
+          <t>165190</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>205025</t>
+          <t>207928</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>258727</t>
+          <t>260565</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>344286</t>
+          <t>342799</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>409924</t>
+          <t>409031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>507593</t>
+          <t>507485</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>551168</t>
+          <t>548998</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>597728</t>
+          <t>595890</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>651430</t>
+          <t>648527</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1119206</t>
+          <t>1120099</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1184844</t>
+          <t>1186331</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,58%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>498707</t>
+          <t>498664</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>579750</t>
+          <t>585848</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>710346</t>
+          <t>705160</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>800129</t>
+          <t>801015</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1229084</t>
+          <t>1231143</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1358587</t>
+          <t>1358193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1884733</t>
+          <t>1878635</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1965776</t>
+          <t>1965819</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2073324</t>
+          <t>2072438</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2163107</t>
+          <t>2168293</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3979349</t>
+          <t>3979743</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4108852</t>
+          <t>4106793</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,94%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2012</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>288442</t>
+          <t>286694</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>335629</t>
+          <t>335216</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>316419</t>
+          <t>314919</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>366594</t>
+          <t>364604</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>617234</t>
+          <t>616398</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>687794</t>
+          <t>689275</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>253051</t>
+          <t>253464</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>300238</t>
+          <t>301986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250348</t>
+          <t>252338</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300523</t>
+          <t>302023</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>517828</t>
+          <t>516347</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>588388</t>
+          <t>589224</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,87%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>421377</t>
+          <t>422828</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>481133</t>
+          <t>483083</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>488176</t>
+          <t>489185</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>547896</t>
+          <t>549638</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>928702</t>
+          <t>927590</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1013787</t>
+          <t>1012778</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,16%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>341165</t>
+          <t>339215</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>400921</t>
+          <t>399470</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>371191</t>
+          <t>369449</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>430911</t>
+          <t>429902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>727598</t>
+          <t>728607</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>812683</t>
+          <t>813795</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,73%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>297808</t>
+          <t>299899</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>349394</t>
+          <t>350985</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>369923</t>
+          <t>373140</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>427255</t>
+          <t>424798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>684711</t>
+          <t>687333</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>758764</t>
+          <t>761556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,63%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>239459</t>
+          <t>237868</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>291045</t>
+          <t>288954</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>261000</t>
+          <t>263457</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>318332</t>
+          <t>315115</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>518344</t>
+          <t>515552</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>592397</t>
+          <t>589775</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,18%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>308810</t>
+          <t>308401</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>364763</t>
+          <t>365182</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>412987</t>
+          <t>412430</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>473739</t>
+          <t>477110</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>736406</t>
+          <t>735270</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>817812</t>
+          <t>820225</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>383628</t>
+          <t>383209</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>439581</t>
+          <t>439990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>445558</t>
+          <t>442187</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>506310</t>
+          <t>506867</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>849876</t>
+          <t>847463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>931282</t>
+          <t>932418</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,91%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1368979</t>
+          <t>1366860</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1478154</t>
+          <t>1474978</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1645976</t>
+          <t>1642075</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1756874</t>
+          <t>1759869</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3045590</t>
+          <t>3046118</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3212455</t>
+          <t>3207681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,44%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1270068</t>
+          <t>1273244</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1379243</t>
+          <t>1381362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1386707</t>
+          <t>1383712</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1497605</t>
+          <t>1501506</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2679348</t>
+          <t>2684122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2846213</t>
+          <t>2845685</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2016</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>222626</t>
+          <t>225300</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>268828</t>
+          <t>269318</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>248249</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>292163</t>
+          <t>293233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>484634</t>
+          <t>483655</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>551009</t>
+          <t>549049</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,54%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>237529</t>
+          <t>237039</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>283731</t>
+          <t>281057</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266793</t>
+          <t>265723</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312606</t>
+          <t>310707</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>514304</t>
+          <t>516264</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>580679</t>
+          <t>581658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,6%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>305508</t>
+          <t>302393</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>360351</t>
+          <t>361732</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>417219</t>
+          <t>414502</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>475369</t>
+          <t>476676</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>738281</t>
+          <t>740223</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>821186</t>
+          <t>818550</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,25%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401032</t>
+          <t>399651</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>455875</t>
+          <t>458990</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>425144</t>
+          <t>423837</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>483294</t>
+          <t>486011</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>840710</t>
+          <t>843346</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>923615</t>
+          <t>921673</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,46%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>163619</t>
+          <t>163428</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>209630</t>
+          <t>211200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>235832</t>
+          <t>240132</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>288178</t>
+          <t>289339</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>416487</t>
+          <t>413807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>482215</t>
+          <t>481821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>336812</t>
+          <t>335242</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>382823</t>
+          <t>383014</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>351778</t>
+          <t>350617</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>404124</t>
+          <t>399824</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>704184</t>
+          <t>704578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>769912</t>
+          <t>772592</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,12%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>252628</t>
+          <t>249749</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>300574</t>
+          <t>301625</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>377075</t>
+          <t>377874</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>437486</t>
+          <t>438486</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>647463</t>
+          <t>645000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>726228</t>
+          <t>724489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,09%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>384237</t>
+          <t>383186</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>432183</t>
+          <t>435062</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>416211</t>
+          <t>415211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>476622</t>
+          <t>475823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>812280</t>
+          <t>814019</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>891045</t>
+          <t>893508</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>58,08%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>987571</t>
+          <t>992738</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1086042</t>
+          <t>1089928</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1331846</t>
+          <t>1332406</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1444516</t>
+          <t>1446870</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2350037</t>
+          <t>2355148</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2502291</t>
+          <t>2502314</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1412951</t>
+          <t>1409065</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1511422</t>
+          <t>1506255</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1508607</t>
+          <t>1506253</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1621277</t>
+          <t>1620717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2949825</t>
+          <t>2949802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3102079</t>
+          <t>3096968</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2023</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85895</t>
+          <t>83555</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119802</t>
+          <t>119100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>101643</t>
+          <t>99580</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>157868</t>
+          <t>155920</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>202702</t>
+          <t>196314</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>264475</t>
+          <t>265057</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>303788</t>
+          <t>304490</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>337695</t>
+          <t>340035</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>412922</t>
+          <t>414870</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>469147</t>
+          <t>471210</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>729906</t>
+          <t>729324</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>791679</t>
+          <t>798067</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>80,26%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>140914</t>
+          <t>140747</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>187832</t>
+          <t>188639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>228710</t>
+          <t>228508</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>271332</t>
+          <t>271514</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>383929</t>
+          <t>382769</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>448559</t>
+          <t>446459</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>450780</t>
+          <t>449973</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>497698</t>
+          <t>497865</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>474769</t>
+          <t>474587</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>517391</t>
+          <t>517593</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>936154</t>
+          <t>938254</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1000784</t>
+          <t>1001944</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,36%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87126</t>
+          <t>87589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127601</t>
+          <t>128159</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>163599</t>
+          <t>164740</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>578370</t>
+          <t>577494</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>267369</t>
+          <t>269133</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>756915</t>
+          <t>766872</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>60,37%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>359727</t>
+          <t>359169</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>400202</t>
+          <t>399739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>204564</t>
+          <t>205440</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>619335</t>
+          <t>618194</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>513346</t>
+          <t>503389</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1002892</t>
+          <t>1001128</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,81%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106622</t>
+          <t>107178</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>145667</t>
+          <t>147523</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145719</t>
+          <t>133447</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>214895</t>
+          <t>211430</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>263167</t>
+          <t>260888</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>346920</t>
+          <t>344217</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>474190</t>
+          <t>472334</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>513235</t>
+          <t>512679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>618992</t>
+          <t>622457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>688168</t>
+          <t>700440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1106824</t>
+          <t>1109527</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1190577</t>
+          <t>1192856</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>458338</t>
+          <t>456947</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>541364</t>
+          <t>536612</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>733652</t>
+          <t>735655</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1372674</t>
+          <t>1404661</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1224278</t>
+          <t>1219515</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1953711</t>
+          <t>1961677</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1628023</t>
+          <t>1632775</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1711049</t>
+          <t>1712440</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1561038</t>
+          <t>1529051</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2200060</t>
+          <t>2198057</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3149388</t>
+          <t>3141422</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3878821</t>
+          <t>3883584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2B_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98259</t>
+          <t>99405</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>136280</t>
+          <t>136998</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131267</t>
+          <t>131340</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>172080</t>
+          <t>173487</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>242571</t>
+          <t>242692</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>298470</t>
+          <t>298568</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>394072</t>
+          <t>393354</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>432093</t>
+          <t>430947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>415484</t>
+          <t>414077</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>456297</t>
+          <t>456224</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>819446</t>
+          <t>819348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>875345</t>
+          <t>875224</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,29%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>147572</t>
+          <t>148477</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>193840</t>
+          <t>194054</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>194743</t>
+          <t>191036</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>246826</t>
+          <t>243920</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>349270</t>
+          <t>354376</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>424594</t>
+          <t>426757</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>553785</t>
+          <t>553571</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>600053</t>
+          <t>599148</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>599774</t>
+          <t>602680</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>651857</t>
+          <t>655564</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1169631</t>
+          <t>1167468</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1244955</t>
+          <t>1239849</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,77%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91281</t>
+          <t>90789</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>128871</t>
+          <t>127393</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127624</t>
+          <t>126933</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>169927</t>
+          <t>169415</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>227862</t>
+          <t>228084</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>285930</t>
+          <t>287424</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>384960</t>
+          <t>386438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>422550</t>
+          <t>423042</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>412908</t>
+          <t>413420</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455211</t>
+          <t>455902</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>810736</t>
+          <t>809242</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>868804</t>
+          <t>868582</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,2%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>123677</t>
+          <t>120685</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>165190</t>
+          <t>163154</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>207928</t>
+          <t>208115</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>260565</t>
+          <t>260418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>342799</t>
+          <t>343594</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>409031</t>
+          <t>410980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>507485</t>
+          <t>509521</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>548998</t>
+          <t>551990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>595890</t>
+          <t>596037</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>648527</t>
+          <t>648340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1120099</t>
+          <t>1118150</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1186331</t>
+          <t>1185536</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,53%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>498664</t>
+          <t>494437</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>585848</t>
+          <t>581117</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>705160</t>
+          <t>705373</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>801015</t>
+          <t>797847</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1231143</t>
+          <t>1230628</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1358193</t>
+          <t>1358434</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1878635</t>
+          <t>1883366</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1965819</t>
+          <t>1970046</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2072438</t>
+          <t>2075606</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2168293</t>
+          <t>2168080</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3979743</t>
+          <t>3979502</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4106793</t>
+          <t>4107308</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>286694</t>
+          <t>286149</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>335216</t>
+          <t>336288</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>314919</t>
+          <t>314245</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>364604</t>
+          <t>367659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>616398</t>
+          <t>615175</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>689275</t>
+          <t>688235</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,09%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>253464</t>
+          <t>252392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>301986</t>
+          <t>302531</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252338</t>
+          <t>249283</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302023</t>
+          <t>302697</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>516347</t>
+          <t>517387</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>589224</t>
+          <t>590447</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,97%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>422828</t>
+          <t>420738</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>483083</t>
+          <t>482720</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>489185</t>
+          <t>488106</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>549638</t>
+          <t>552930</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>927590</t>
+          <t>927974</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1012778</t>
+          <t>1015504</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,32%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>339215</t>
+          <t>339578</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399470</t>
+          <t>401560</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>369449</t>
+          <t>366157</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>429902</t>
+          <t>430981</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>728607</t>
+          <t>725881</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>813795</t>
+          <t>813411</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,71%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>299899</t>
+          <t>298571</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>350985</t>
+          <t>349950</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>373140</t>
+          <t>372506</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>424798</t>
+          <t>427143</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>687333</t>
+          <t>686380</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>761556</t>
+          <t>761238</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,61%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>237868</t>
+          <t>238903</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>288954</t>
+          <t>290282</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>263457</t>
+          <t>261112</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>315115</t>
+          <t>315749</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>515552</t>
+          <t>515870</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>589775</t>
+          <t>590728</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,26%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>308401</t>
+          <t>310837</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>365182</t>
+          <t>365047</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>412430</t>
+          <t>417127</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>477110</t>
+          <t>475845</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>735270</t>
+          <t>739912</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>820225</t>
+          <t>820034</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>383209</t>
+          <t>383344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>439990</t>
+          <t>437554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>442187</t>
+          <t>443452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>506867</t>
+          <t>502170</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>847463</t>
+          <t>847654</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>932418</t>
+          <t>927776</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,63%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1366860</t>
+          <t>1366682</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1474978</t>
+          <t>1477050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1642075</t>
+          <t>1646138</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1759869</t>
+          <t>1755358</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3046118</t>
+          <t>3038954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3207681</t>
+          <t>3202251</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,35%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1273244</t>
+          <t>1271172</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1381362</t>
+          <t>1381540</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1383712</t>
+          <t>1388223</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1501506</t>
+          <t>1497443</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2684122</t>
+          <t>2689552</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2845685</t>
+          <t>2852849</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,42%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>225300</t>
+          <t>224443</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>269318</t>
+          <t>269381</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>248249</t>
+          <t>249490</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>293233</t>
+          <t>299992</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>483655</t>
+          <t>485012</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>549049</t>
+          <t>548254</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,46%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>237039</t>
+          <t>236976</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281057</t>
+          <t>281914</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265723</t>
+          <t>258964</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310707</t>
+          <t>309466</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>516264</t>
+          <t>517059</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>581658</t>
+          <t>580301</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,47%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>302393</t>
+          <t>305744</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>361732</t>
+          <t>358885</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>414502</t>
+          <t>416932</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>476676</t>
+          <t>476865</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>740223</t>
+          <t>737057</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>818550</t>
+          <t>819824</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,33%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399651</t>
+          <t>402498</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>458990</t>
+          <t>455639</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>423837</t>
+          <t>423648</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>486011</t>
+          <t>483581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>843346</t>
+          <t>842072</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>921673</t>
+          <t>924839</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,65%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>163428</t>
+          <t>163815</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>211200</t>
+          <t>209499</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>240132</t>
+          <t>238669</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>289339</t>
+          <t>289831</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>413807</t>
+          <t>413925</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>481821</t>
+          <t>482118</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>335242</t>
+          <t>336943</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>383014</t>
+          <t>382627</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>350617</t>
+          <t>350125</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>399824</t>
+          <t>401287</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>704578</t>
+          <t>704281</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>772592</t>
+          <t>772474</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,11%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>249749</t>
+          <t>249905</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>301625</t>
+          <t>300436</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>377874</t>
+          <t>377928</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>438486</t>
+          <t>436461</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>645000</t>
+          <t>646545</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>724489</t>
+          <t>725271</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,14%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>383186</t>
+          <t>384375</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>435062</t>
+          <t>434906</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>415211</t>
+          <t>417236</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>475823</t>
+          <t>475769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>814019</t>
+          <t>813237</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>893508</t>
+          <t>891963</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,98%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>992738</t>
+          <t>989298</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1089928</t>
+          <t>1093685</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1332406</t>
+          <t>1329864</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1446870</t>
+          <t>1438320</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2355148</t>
+          <t>2346271</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2502314</t>
+          <t>2495542</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1409065</t>
+          <t>1405308</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1506255</t>
+          <t>1509695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1506253</t>
+          <t>1514803</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1620717</t>
+          <t>1623259</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2949802</t>
+          <t>2956574</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3096968</t>
+          <t>3105845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>101088</t>
+          <t>109490</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83555</t>
+          <t>91690</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119100</t>
+          <t>129589</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>136452</t>
+          <t>148346</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99580</t>
+          <t>130626</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>155920</t>
+          <t>164695</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>237541</t>
+          <t>257836</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>196314</t>
+          <t>233600</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>265057</t>
+          <t>285526</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>322502</t>
+          <t>349541</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>304490</t>
+          <t>329442</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>340035</t>
+          <t>367341</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>434338</t>
+          <t>422194</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>414870</t>
+          <t>405845</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>471210</t>
+          <t>439914</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>756840</t>
+          <t>771734</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>729324</t>
+          <t>744044</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>798067</t>
+          <t>795970</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>77,31%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>423590</t>
+          <t>459031</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>423590</t>
+          <t>459031</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>423590</t>
+          <t>459031</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>570790</t>
+          <t>570540</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>570790</t>
+          <t>570540</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>570790</t>
+          <t>570540</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>994381</t>
+          <t>1029570</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>994381</t>
+          <t>1029570</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>994381</t>
+          <t>1029570</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>163817</t>
+          <t>197036</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>140747</t>
+          <t>173178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>188639</t>
+          <t>225201</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>249692</t>
+          <t>279379</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>228508</t>
+          <t>256929</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>271514</t>
+          <t>303942</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>413509</t>
+          <t>476415</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>382769</t>
+          <t>440893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>446459</t>
+          <t>513511</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>474795</t>
+          <t>506934</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>449973</t>
+          <t>478769</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>497865</t>
+          <t>530792</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>496409</t>
+          <t>559196</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>474587</t>
+          <t>534633</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>517593</t>
+          <t>581646</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>971204</t>
+          <t>1066130</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>938254</t>
+          <t>1029034</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1001944</t>
+          <t>1101652</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>71,42%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>638612</t>
+          <t>703970</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>638612</t>
+          <t>703970</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>638612</t>
+          <t>703970</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>746101</t>
+          <t>838575</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>746101</t>
+          <t>838575</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>746101</t>
+          <t>838575</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1384713</t>
+          <t>1542545</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1384713</t>
+          <t>1542545</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1384713</t>
+          <t>1542545</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>106376</t>
+          <t>123968</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87589</t>
+          <t>102381</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>128159</t>
+          <t>146015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>333130</t>
+          <t>155875</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>164740</t>
+          <t>135819</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>577494</t>
+          <t>179858</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>439505</t>
+          <t>279843</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>269133</t>
+          <t>250600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>766872</t>
+          <t>309932</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>380952</t>
+          <t>433850</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>359169</t>
+          <t>411803</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>399739</t>
+          <t>455437</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>449804</t>
+          <t>488356</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>205440</t>
+          <t>464373</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>618194</t>
+          <t>508412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>830756</t>
+          <t>922206</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>503389</t>
+          <t>892117</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1001128</t>
+          <t>951449</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>79,15%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>487328</t>
+          <t>557818</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>487328</t>
+          <t>557818</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>487328</t>
+          <t>557818</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>782934</t>
+          <t>644231</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>782934</t>
+          <t>644231</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>782934</t>
+          <t>644231</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1270261</t>
+          <t>1202049</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1270261</t>
+          <t>1202049</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1270261</t>
+          <t>1202049</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>124889</t>
+          <t>140755</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107178</t>
+          <t>118365</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>147523</t>
+          <t>161942</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>185687</t>
+          <t>214931</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>133447</t>
+          <t>193870</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>211430</t>
+          <t>238382</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>310576</t>
+          <t>355686</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>260888</t>
+          <t>326320</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>344217</t>
+          <t>385307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>494968</t>
+          <t>513867</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>472334</t>
+          <t>492680</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>512679</t>
+          <t>536257</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>648200</t>
+          <t>613075</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>622457</t>
+          <t>589624</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>700440</t>
+          <t>634136</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1143168</t>
+          <t>1126942</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1109527</t>
+          <t>1097321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1192856</t>
+          <t>1156308</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>77,99%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>619857</t>
+          <t>654622</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>619857</t>
+          <t>654622</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>619857</t>
+          <t>654622</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>833887</t>
+          <t>828006</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>833887</t>
+          <t>828006</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>833887</t>
+          <t>828006</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1453744</t>
+          <t>1482628</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1453744</t>
+          <t>1482628</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1453744</t>
+          <t>1482628</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>496170</t>
+          <t>571250</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>456947</t>
+          <t>526661</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>536612</t>
+          <t>616392</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>904961</t>
+          <t>798531</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>735655</t>
+          <t>761055</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1404661</t>
+          <t>840593</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1401131</t>
+          <t>1369781</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1219515</t>
+          <t>1311410</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1961677</t>
+          <t>1430828</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1673217</t>
+          <t>1804190</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1632775</t>
+          <t>1759048</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1712440</t>
+          <t>1848779</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2028751</t>
+          <t>2082821</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1529051</t>
+          <t>2040759</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2198057</t>
+          <t>2120297</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3701968</t>
+          <t>3887011</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3141422</t>
+          <t>3825964</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3883584</t>
+          <t>3945382</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,05%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2169387</t>
+          <t>2375440</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2169387</t>
+          <t>2375440</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2169387</t>
+          <t>2375440</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2933712</t>
+          <t>2881352</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2933712</t>
+          <t>2881352</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2933712</t>
+          <t>2881352</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>5103099</t>
+          <t>5256792</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5103099</t>
+          <t>5256792</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5103099</t>
+          <t>5256792</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P2B_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2023 (tasa de respuesta: 99,84%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
